--- a/title_optimization_titles.xlsx
+++ b/title_optimization_titles.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +51,11 @@
         <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B084"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -64,12 +69,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1443,45 +1449,45 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>DG94-03575A</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03575A</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03575A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03575A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03575A</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03575A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03575A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -2303,45 +2309,45 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>AGM75549801</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - AGM75549801</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - AGM75549801 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Shop LG Replacement Part - AGM75549801. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>LG Range Control Panel - AGM75549801</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>LG Range Control Panel - AGM75549801 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Shop LG Range Control Panel - AGM75549801. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -2475,131 +2481,131 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>DE92-03967A</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DE92-03967A</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DE92-03967A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DE92-03967A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G48" s="2" t="n">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Control Board - DE92-03967A</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Control Board - DE92-03967A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Control Board - DE92-03967A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="G48" s="5" t="n">
         <v>119</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>DG96-00427A</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG96-00427A</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG96-00427A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG96-00427A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G49" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG96-00427A</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG96-00427A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG96-00427A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>DE96-01050B</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DE96-01050B</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DE96-01050B | OEM Part</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DE96-01050B. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Control Module Assembly - DE96-01050B</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Control Module Assembly - DE96-01050B | OEM Part</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Control Module Assembly - DE96-01050B. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -2647,45 +2653,45 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>DG94-01281B</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01281B</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01281B | OEM Part</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-01281B. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01281B</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01281B | OEM Part</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-01281B. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -2991,45 +2997,45 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>AGU74969001</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - AGU74969001</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - AGU74969001 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Shop LG Replacement Part - AGU74969001. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>LG Range Plate Assembly - AGU74969001</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>LG Range Plate Assembly - AGU74969001 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>Shop LG Range Plate Assembly - AGU74969001. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -3206,45 +3212,45 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>MEB63654001</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - MEB63654001</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - MEB63654001 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Shop LG Replacement Part - MEB63654001. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>LG Handle - MEB63654001</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>LG Handle - MEB63654001 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Shop LG Handle - MEB63654001. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -3378,45 +3384,45 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>DG94-01961A</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01961A</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01961A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-01961A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G69" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01961A</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01961A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-01961A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -3464,45 +3470,45 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>DG94-01994A</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01994A</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01994A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-01994A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G71" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01994A</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01994A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-01994A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -3636,88 +3642,88 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>DG94-04247B</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04247B</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04247B | OEM Part</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-04247B. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04247B</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04247B | OEM Part</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-04247B. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>DG94-03701A</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03701A</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03701A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03701A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G76" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03701A</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03701A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03701A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -3765,45 +3771,45 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>DG94-01141E</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01141E</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01141E | OEM Part</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-01141E. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G78" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01141E</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01141E | OEM Part</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-01141E. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -3851,88 +3857,88 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>DG94-01727C</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01727C</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01727C | OEM Part</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-01727C. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G80" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01727C</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01727C | OEM Part</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-01727C. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>DG96-00728A</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG96-00728A</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG96-00728A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG96-00728A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G81" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG96-00728A</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG96-00728A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG96-00728A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -3980,45 +3986,45 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>DG94-02881D</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-02881D</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-02881D | OEM Part</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-02881D. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-02881D</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-02881D | OEM Part</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-02881D. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -4066,131 +4072,131 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>DG94-03551K</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03551K</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03551K | OEM Part</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03551K. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G85" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03551K</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03551K | OEM Part</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03551K. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>DG96-00773L</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG96-00773L</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG96-00773L | OEM Part</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG96-00773L. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G86" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG96-00773L</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG96-00773L | OEM Part</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG96-00773L. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>DG90-01358D</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG90-01358D</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG90-01358D | OEM Part</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG90-01358D. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G87" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Drawer Main Module Assembly - DG90-01358D</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Drawer Main Module Assembly - DG90-01358D | OEM Part</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Drawer Main Module Assembly - DG90-01358D. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -4281,45 +4287,45 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>DG94-03552C</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03552C</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03552C | OEM Part</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03552C. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03552C</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03552C | OEM Part</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03552C. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -4367,174 +4373,174 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>DG94-02896A</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-02896A</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-02896A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-02896A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G92" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-02896A</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-02896A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-02896A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>DG90-01193C</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG90-01193C</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG90-01193C | OEM Part</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG90-01193C. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G93" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Drawer Main Module Assembly - DG90-01193C</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Drawer Main Module Assembly - DG90-01193C | OEM Part</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Drawer Main Module Assembly - DG90-01193C. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>DG90-01232B</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG90-01232B</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG90-01232B | OEM Part</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG90-01232B. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G94" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Drawer Main Module Assembly - DG90-01232B</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Drawer Main Module Assembly - DG90-01232B | OEM Part</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Drawer Main Module Assembly - DG90-01232B. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>DG94-04664L</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04664L</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04664L | OEM Part</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-04664L. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G95" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04664L</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04664L | OEM Part</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-04664L. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -4582,45 +4588,45 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>DG90-01184C</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG90-01184C</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG90-01184C | OEM Part</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG90-01184C. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G97" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Drawer Main Module Assembly - DG90-01184C</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Drawer Main Module Assembly - DG90-01184C | OEM Part</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Drawer Main Module Assembly - DG90-01184C. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -4668,45 +4674,45 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>DG94-04664B</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04664B</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04664B | OEM Part</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-04664B. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04664B</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04664B | OEM Part</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-04664B. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -4754,131 +4760,131 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>DG94-05016A</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-05016A</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-05016A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-05016A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G101" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-05016A</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-05016A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-05016A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>DG94-02881C</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-02881C</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-02881C | OEM Part</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-02881C. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-02881C</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-02881C | OEM Part</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-02881C. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" s="5" t="inlineStr">
         <is>
           <t>DG94-03551D</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B103" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03551D</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03551D | OEM Part</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03551D. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G103" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03551D</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03551D | OEM Part</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03551D. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -4926,174 +4932,174 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="A105" s="5" t="inlineStr">
         <is>
           <t>DG94-04664H</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B105" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04664H</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04664H | OEM Part</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-04664H. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G105" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04664H</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04664H | OEM Part</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-04664H. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="A106" s="5" t="inlineStr">
         <is>
           <t>DG94-03952T</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B106" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03952T</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03952T | OEM Part</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03952T. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03952T</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03952T | OEM Part</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03952T. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="A107" s="5" t="inlineStr">
         <is>
           <t>DG90-01232A</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG90-01232A</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG90-01232A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG90-01232A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G107" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Drawer Main Module Assembly - DG90-01232A</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Drawer Main Module Assembly - DG90-01232A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Drawer Main Module Assembly - DG90-01232A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>DG94-04148C</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04148C</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04148C | OEM Part</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-04148C. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G108" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04148C</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04148C | OEM Part</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-04148C. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -5485,131 +5491,131 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>AHB73129211</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B118" s="5" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - AHB73129211</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - AHB73129211 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>Shop LG Replacement Part - AHB73129211. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>LG Dishwasher Rack Assembly - AHB73129211</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>LG Dishwasher Rack Assembly - AHB73129211 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>Shop LG Dishwasher Rack Assembly - AHB73129211. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="A119" s="5" t="inlineStr">
         <is>
           <t>AGU75049016</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B119" s="5" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - AGU75049016</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - AGU75049016 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>Shop LG Replacement Part - AGU75049016. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G119" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>LG Range Plate Assembly - AGU75049016</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>LG Range Plate Assembly - AGU75049016 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>Shop LG Range Plate Assembly - AGU75049016. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="A120" s="5" t="inlineStr">
         <is>
           <t>DG98-01358A</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B120" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG98-01358A</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG98-01358A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG98-01358A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G120" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Cooktop Burner Grate - DG98-01358A</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Cooktop Burner Grate - DG98-01358A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Cooktop Burner Grate - DG98-01358A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -6044,45 +6050,45 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="A131" s="5" t="inlineStr">
         <is>
           <t>DG94-04293A</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B131" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04293A</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04293A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-04293A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G131" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04293A</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04293A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-04293A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -6130,88 +6136,88 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="A133" s="5" t="inlineStr">
         <is>
           <t>DG94-03584A</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B133" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03584A</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03584A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03584A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G133" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03584A</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03584A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03584A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="A134" s="5" t="inlineStr">
         <is>
           <t>DG94-03580B</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03580B</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03580B | OEM Part</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03580B. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G134" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03580B</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03580B | OEM Part</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03580B. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -6345,45 +6351,45 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="A138" s="5" t="inlineStr">
         <is>
           <t>DG94-00513A</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B138" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-00513A</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-00513A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-00513A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G138" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-00513A</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-00513A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-00513A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -6603,45 +6609,45 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="A144" s="5" t="inlineStr">
         <is>
           <t>DG94-04108B</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B144" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04108B</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04108B | OEM Part</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-04108B. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G144" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04108B</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04108B | OEM Part</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-04108B. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I144" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -6689,88 +6695,88 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="A146" s="5" t="inlineStr">
         <is>
           <t>DG94-01301C</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B146" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01301C</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01301C | OEM Part</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-01301C. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G146" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I146" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01301C</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01301C | OEM Part</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-01301C. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="A147" s="5" t="inlineStr">
         <is>
           <t>DG96-00528A</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B147" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG96-00528A</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG96-00528A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG96-00528A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G147" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG96-00528A</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG96-00528A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG96-00528A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I147" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -6818,88 +6824,88 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="A149" s="5" t="inlineStr">
         <is>
           <t>DG94-03551C</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B149" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03551C</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03551C | OEM Part</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03551C. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03551C</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03551C | OEM Part</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03551C. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t>DG94-03551A</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B150" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03551A</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03551A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03551A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G150" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03551A</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03551A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03551A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H150" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I150" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -6947,45 +6953,45 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="A152" s="5" t="inlineStr">
         <is>
           <t>DG94-03552K</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B152" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03552K</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03552K | OEM Part</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03552K. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03552K</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03552K | OEM Part</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03552K. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I152" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -7033,88 +7039,88 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="A154" s="5" t="inlineStr">
         <is>
           <t>DG94-03598B</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B154" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03598B</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03598B | OEM Part</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03598B. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G154" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03598B</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03598B | OEM Part</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03598B. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H154" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I154" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="A155" s="5" t="inlineStr">
         <is>
           <t>DE94-05320A</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B155" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DE94-05320A</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DE94-05320A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DE94-05320A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G155" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Microwave Assembly - DE94-05320A</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Microwave Assembly - DE94-05320A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Microwave Assembly - DE94-05320A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I155" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -7248,88 +7254,88 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="A159" s="5" t="inlineStr">
         <is>
           <t>DG94-05016D</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B159" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-05016D</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-05016D | OEM Part</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-05016D. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G159" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-05016D</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-05016D | OEM Part</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-05016D. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="A160" s="5" t="inlineStr">
         <is>
           <t>DG94-02672A</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B160" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-02672A</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-02672A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-02672A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G160" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I160" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-02672A</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-02672A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-02672A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H160" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -7377,260 +7383,260 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="A162" s="5" t="inlineStr">
         <is>
           <t>DG94-03549N</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B162" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03549N</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03549N | OEM Part</t>
-        </is>
-      </c>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03549N. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G162" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03549N</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03549N | OEM Part</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03549N. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H162" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I162" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="A163" s="5" t="inlineStr">
         <is>
           <t>DG94-03952W</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B163" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03952W</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03952W | OEM Part</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03952W. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G163" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03952W</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03952W | OEM Part</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03952W. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I163" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="A164" s="5" t="inlineStr">
         <is>
           <t>DG94-03952P</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B164" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03952P</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03952P | OEM Part</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03952P. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G164" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03952P</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03952P | OEM Part</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03952P. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I164" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="A165" s="5" t="inlineStr">
         <is>
           <t>DG94-03577D</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B165" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03577D</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03577D | OEM Part</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03577D. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G165" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03577D</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03577D | OEM Part</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03577D. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I165" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="A166" s="5" t="inlineStr">
         <is>
           <t>DE94-05062B</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B166" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DE94-05062B</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DE94-05062B | OEM Part</t>
-        </is>
-      </c>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DE94-05062B. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G166" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Microwave Assembly - DE94-05062B</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Microwave Assembly - DE94-05062B | OEM Part</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Microwave Assembly - DE94-05062B. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="H166" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I166" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="A167" s="5" t="inlineStr">
         <is>
           <t>DG94-03580A</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B167" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03580A</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03580A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03580A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G167" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03580A</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03580A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03580A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I167" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -7678,217 +7684,217 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="A169" s="5" t="inlineStr">
         <is>
           <t>DG94-01727E</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B169" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01727E</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01727E | OEM Part</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-01727E. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F169" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G169" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01727E</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01727E | OEM Part</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-01727E. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I169" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="A170" s="5" t="inlineStr">
         <is>
           <t>DG94-03982A</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B170" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03982A</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-03982A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-03982A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G170" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I170" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03982A</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-03982A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-03982A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H170" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I170" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="A171" s="5" t="inlineStr">
         <is>
           <t>DE94-05062C</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B171" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DE94-05062C</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DE94-05062C | OEM Part</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DE94-05062C. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F171" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G171" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Microwave Assembly - DE94-05062C</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Microwave Assembly - DE94-05062C | OEM Part</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Microwave Assembly - DE94-05062C. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F171" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I171" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="A172" s="5" t="inlineStr">
         <is>
           <t>DG90-01184A</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B172" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG90-01184A</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG90-01184A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E172" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG90-01184A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G172" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I172" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Drawer Main Module Assembly - DG90-01184A</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Drawer Main Module Assembly - DG90-01184A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Drawer Main Module Assembly - DG90-01184A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="H172" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I172" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="A173" s="5" t="inlineStr">
         <is>
           <t>DG94-04089A</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B173" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04089A</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04089A | OEM Part</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-04089A. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F173" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G173" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04089A</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04089A | OEM Part</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-04089A. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I173" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -8753,45 +8759,45 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+      <c r="A194" s="5" t="inlineStr">
         <is>
           <t>DE92-02439F</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
+      <c r="B194" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DE92-02439F</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DE92-02439F | OEM Part</t>
-        </is>
-      </c>
-      <c r="E194" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DE92-02439F. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F194" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G194" s="2" t="n">
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Control Board - DE92-02439F</t>
+        </is>
+      </c>
+      <c r="D194" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Control Board - DE92-02439F | OEM Part</t>
+        </is>
+      </c>
+      <c r="E194" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Control Board - DE92-02439F. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F194" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="G194" s="5" t="n">
         <v>119</v>
       </c>
-      <c r="H194" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I194" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="H194" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I194" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -8882,45 +8888,45 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+      <c r="A197" s="5" t="inlineStr">
         <is>
           <t>MEE62306301</t>
         </is>
       </c>
-      <c r="B197" s="2" t="inlineStr">
+      <c r="B197" s="5" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - MEE62306301</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - MEE62306301 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E197" s="2" t="inlineStr">
-        <is>
-          <t>Shop LG Replacement Part - MEE62306301. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F197" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G197" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="H197" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I197" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t>LG Range Heating Element - MEE62306301</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>LG Range Heating Element - MEE62306301 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="inlineStr">
+        <is>
+          <t>Shop LG Range Heating Element - MEE62306301. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F197" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="G197" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="H197" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I197" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -9226,45 +9232,45 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+      <c r="A205" s="5" t="inlineStr">
         <is>
           <t>DG94-04148E</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
+      <c r="B205" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04148E</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04148E | OEM Part</t>
-        </is>
-      </c>
-      <c r="E205" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-04148E. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F205" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G205" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H205" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I205" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04148E</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04148E | OEM Part</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-04148E. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F205" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G205" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H205" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I205" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -9484,131 +9490,131 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="inlineStr">
+      <c r="A211" s="5" t="inlineStr">
         <is>
           <t>EBR87050404</t>
         </is>
       </c>
-      <c r="B211" s="2" t="inlineStr">
+      <c r="B211" s="5" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - EBR87050404</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - EBR87050404 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E211" s="2" t="inlineStr">
-        <is>
-          <t>Shop LG Replacement Part - EBR87050404. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F211" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G211" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="H211" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I211" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>LG PCB Control Board - EBR87050404</t>
+        </is>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>LG PCB Control Board - EBR87050404 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="inlineStr">
+        <is>
+          <t>Shop LG PCB Control Board - EBR87050404. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F211" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="G211" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="H211" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I211" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+      <c r="A212" s="5" t="inlineStr">
         <is>
           <t>EBR87050401</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
+      <c r="B212" s="5" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - EBR87050401</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - EBR87050401 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E212" s="2" t="inlineStr">
-        <is>
-          <t>Shop LG Replacement Part - EBR87050401. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F212" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G212" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="H212" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I212" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>LG PCB Control Board - EBR87050401</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
+        <is>
+          <t>LG PCB Control Board - EBR87050401 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E212" s="5" t="inlineStr">
+        <is>
+          <t>Shop LG PCB Control Board - EBR87050401. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F212" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="G212" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="H212" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I212" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+      <c r="A213" s="5" t="inlineStr">
         <is>
           <t>EBR85707901</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
+      <c r="B213" s="5" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - EBR85707901</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - EBR85707901 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E213" s="2" t="inlineStr">
-        <is>
-          <t>Shop LG Replacement Part - EBR85707901. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F213" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G213" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="H213" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I213" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>LG PCB Control Board - EBR85707901</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
+        <is>
+          <t>LG PCB Control Board - EBR85707901 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E213" s="5" t="inlineStr">
+        <is>
+          <t>Shop LG PCB Control Board - EBR85707901. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F213" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="G213" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="H213" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I213" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -9656,45 +9662,45 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="inlineStr">
+      <c r="A215" s="5" t="inlineStr">
         <is>
           <t>DG94-01301E</t>
         </is>
       </c>
-      <c r="B215" s="2" t="inlineStr">
+      <c r="B215" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01301E</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01301E | OEM Part</t>
-        </is>
-      </c>
-      <c r="E215" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-01301E. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F215" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G215" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H215" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I215" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01301E</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01301E | OEM Part</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-01301E. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F215" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G215" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H215" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I215" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -10000,131 +10006,131 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+      <c r="A223" s="5" t="inlineStr">
         <is>
           <t>DG92-01198F</t>
         </is>
       </c>
-      <c r="B223" s="2" t="inlineStr">
+      <c r="B223" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG92-01198F</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG92-01198F | OEM Part</t>
-        </is>
-      </c>
-      <c r="E223" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG92-01198F. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F223" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G223" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H223" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I223" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Control Board - DG92-01198F</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Control Board - DG92-01198F | OEM Part</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Control Board - DG92-01198F. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F223" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="G223" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="H223" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I223" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="inlineStr">
+      <c r="A224" s="5" t="inlineStr">
         <is>
           <t>DG94-01548B</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
+      <c r="B224" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01548B</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01548B | OEM Part</t>
-        </is>
-      </c>
-      <c r="E224" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-01548B. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F224" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G224" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H224" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I224" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C224" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01548B</t>
+        </is>
+      </c>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01548B | OEM Part</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-01548B. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F224" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G224" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H224" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I224" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="inlineStr">
+      <c r="A225" s="5" t="inlineStr">
         <is>
           <t>DG94-01545B</t>
         </is>
       </c>
-      <c r="B225" s="2" t="inlineStr">
+      <c r="B225" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01545B</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-01545B | OEM Part</t>
-        </is>
-      </c>
-      <c r="E225" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-01545B. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F225" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G225" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H225" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I225" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C225" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01545B</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-01545B | OEM Part</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-01545B. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F225" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G225" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H225" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I225" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -10172,45 +10178,45 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="inlineStr">
+      <c r="A227" s="5" t="inlineStr">
         <is>
           <t>DG94-04664P</t>
         </is>
       </c>
-      <c r="B227" s="2" t="inlineStr">
+      <c r="B227" s="5" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04664P</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="inlineStr">
-        <is>
-          <t>Samsung Replacement Part - DG94-04664P | OEM Part</t>
-        </is>
-      </c>
-      <c r="E227" s="2" t="inlineStr">
-        <is>
-          <t>Shop Samsung Replacement Part - DG94-04664P. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F227" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="G227" s="2" t="n">
-        <v>119</v>
-      </c>
-      <c r="H227" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I227" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C227" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04664P</t>
+        </is>
+      </c>
+      <c r="D227" s="5" t="inlineStr">
+        <is>
+          <t>Samsung Range Assembly - DG94-04664P | OEM Part</t>
+        </is>
+      </c>
+      <c r="E227" s="5" t="inlineStr">
+        <is>
+          <t>Shop Samsung Range Assembly - DG94-04664P. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F227" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G227" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="H227" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I227" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -11806,45 +11812,45 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="inlineStr">
+      <c r="A265" s="5" t="inlineStr">
         <is>
           <t>318261301</t>
         </is>
       </c>
-      <c r="B265" s="2" t="inlineStr">
+      <c r="B265" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C265" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 318261301</t>
-        </is>
-      </c>
-      <c r="D265" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 318261301 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E265" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 318261301. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F265" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G265" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H265" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I265" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 318261301</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 318261301 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E265" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 318261301. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F265" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G265" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H265" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I265" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -12881,45 +12887,45 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="inlineStr">
+      <c r="A290" s="5" t="inlineStr">
         <is>
           <t>316472803</t>
         </is>
       </c>
-      <c r="B290" s="2" t="inlineStr">
+      <c r="B290" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C290" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316472803</t>
-        </is>
-      </c>
-      <c r="D290" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316472803 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E290" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316472803. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F290" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G290" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H290" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I290" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C290" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316472803</t>
+        </is>
+      </c>
+      <c r="D290" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316472803 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E290" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316472803. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F290" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G290" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H290" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I290" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -13483,174 +13489,174 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="inlineStr">
+      <c r="A304" s="5" t="inlineStr">
         <is>
           <t>316418501</t>
         </is>
       </c>
-      <c r="B304" s="2" t="inlineStr">
+      <c r="B304" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C304" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316418501</t>
-        </is>
-      </c>
-      <c r="D304" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316418501 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E304" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316418501. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F304" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G304" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H304" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I304" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C304" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316418501</t>
+        </is>
+      </c>
+      <c r="D304" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316418501 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E304" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316418501. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F304" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G304" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H304" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I304" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="inlineStr">
+      <c r="A305" s="5" t="inlineStr">
         <is>
           <t>318258201</t>
         </is>
       </c>
-      <c r="B305" s="2" t="inlineStr">
+      <c r="B305" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C305" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 318258201</t>
-        </is>
-      </c>
-      <c r="D305" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 318258201 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E305" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 318258201. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F305" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G305" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H305" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I305" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C305" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 318258201</t>
+        </is>
+      </c>
+      <c r="D305" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 318258201 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E305" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 318258201. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F305" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G305" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H305" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I305" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="inlineStr">
+      <c r="A306" s="5" t="inlineStr">
         <is>
           <t>316456238</t>
         </is>
       </c>
-      <c r="B306" s="2" t="inlineStr">
+      <c r="B306" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C306" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316456238</t>
-        </is>
-      </c>
-      <c r="D306" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316456238 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E306" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316456238. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F306" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G306" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H306" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I306" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C306" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316456238</t>
+        </is>
+      </c>
+      <c r="D306" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316456238 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E306" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316456238. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F306" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G306" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H306" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I306" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="inlineStr">
+      <c r="A307" s="5" t="inlineStr">
         <is>
           <t>318022001</t>
         </is>
       </c>
-      <c r="B307" s="2" t="inlineStr">
+      <c r="B307" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C307" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 318022001</t>
-        </is>
-      </c>
-      <c r="D307" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 318022001 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E307" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 318022001. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F307" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G307" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H307" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I307" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C307" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 318022001</t>
+        </is>
+      </c>
+      <c r="D307" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 318022001 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E307" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 318022001. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F307" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G307" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H307" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I307" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -13999,88 +14005,88 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="inlineStr">
+      <c r="A316" s="5" t="inlineStr">
         <is>
           <t>316531960</t>
         </is>
       </c>
-      <c r="B316" s="2" t="inlineStr">
+      <c r="B316" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C316" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316531960</t>
-        </is>
-      </c>
-      <c r="D316" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316531960 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E316" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316531960. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F316" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G316" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H316" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I316" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C316" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316531960</t>
+        </is>
+      </c>
+      <c r="D316" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316531960 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E316" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316531960. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F316" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G316" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H316" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I316" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="inlineStr">
+      <c r="A317" s="5" t="inlineStr">
         <is>
           <t>316650003</t>
         </is>
       </c>
-      <c r="B317" s="2" t="inlineStr">
+      <c r="B317" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C317" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316650003</t>
-        </is>
-      </c>
-      <c r="D317" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316650003 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E317" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316650003. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F317" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G317" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H317" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I317" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316650003</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316650003 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E317" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316650003. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F317" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G317" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H317" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I317" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -14171,174 +14177,174 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="inlineStr">
+      <c r="A320" s="5" t="inlineStr">
         <is>
           <t>316462865</t>
         </is>
       </c>
-      <c r="B320" s="2" t="inlineStr">
+      <c r="B320" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C320" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316462865</t>
-        </is>
-      </c>
-      <c r="D320" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316462865 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E320" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316462865. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F320" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G320" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H320" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I320" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316462865</t>
+        </is>
+      </c>
+      <c r="D320" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316462865 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E320" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316462865. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F320" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G320" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H320" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I320" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="inlineStr">
+      <c r="A321" s="5" t="inlineStr">
         <is>
           <t>316462890</t>
         </is>
       </c>
-      <c r="B321" s="2" t="inlineStr">
+      <c r="B321" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C321" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316462890</t>
-        </is>
-      </c>
-      <c r="D321" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316462890 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E321" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316462890. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F321" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G321" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H321" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I321" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316462890</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316462890 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E321" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316462890. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F321" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G321" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H321" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I321" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="inlineStr">
+      <c r="A322" s="5" t="inlineStr">
         <is>
           <t>316453036</t>
         </is>
       </c>
-      <c r="B322" s="2" t="inlineStr">
+      <c r="B322" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C322" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316453036</t>
-        </is>
-      </c>
-      <c r="D322" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316453036 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E322" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316453036. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F322" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G322" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H322" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I322" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316453036</t>
+        </is>
+      </c>
+      <c r="D322" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316453036 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E322" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316453036. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F322" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G322" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H322" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I322" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="inlineStr">
+      <c r="A323" s="5" t="inlineStr">
         <is>
           <t>316531983</t>
         </is>
       </c>
-      <c r="B323" s="2" t="inlineStr">
+      <c r="B323" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C323" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316531983</t>
-        </is>
-      </c>
-      <c r="D323" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316531983 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E323" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316531983. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F323" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G323" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H323" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I323" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316531983</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316531983 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E323" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316531983. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F323" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G323" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H323" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I323" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -14429,45 +14435,45 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="inlineStr">
+      <c r="A326" s="5" t="inlineStr">
         <is>
           <t>316462878</t>
         </is>
       </c>
-      <c r="B326" s="2" t="inlineStr">
+      <c r="B326" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C326" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316462878</t>
-        </is>
-      </c>
-      <c r="D326" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316462878 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E326" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316462878. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F326" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G326" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H326" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I326" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C326" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316462878</t>
+        </is>
+      </c>
+      <c r="D326" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316462878 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E326" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316462878. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F326" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G326" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H326" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I326" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -14515,131 +14521,131 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="inlineStr">
+      <c r="A328" s="5" t="inlineStr">
         <is>
           <t>316630001</t>
         </is>
       </c>
-      <c r="B328" s="2" t="inlineStr">
+      <c r="B328" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C328" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316630001</t>
-        </is>
-      </c>
-      <c r="D328" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316630001 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E328" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316630001. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F328" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G328" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H328" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I328" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C328" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316630001</t>
+        </is>
+      </c>
+      <c r="D328" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316630001 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E328" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316630001. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F328" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G328" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H328" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I328" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="inlineStr">
+      <c r="A329" s="5" t="inlineStr">
         <is>
           <t>316650001</t>
         </is>
       </c>
-      <c r="B329" s="2" t="inlineStr">
+      <c r="B329" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C329" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316650001</t>
-        </is>
-      </c>
-      <c r="D329" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316650001 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E329" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316650001. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F329" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G329" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H329" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I329" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C329" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316650001</t>
+        </is>
+      </c>
+      <c r="D329" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316650001 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E329" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316650001. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F329" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G329" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H329" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I329" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="inlineStr">
+      <c r="A330" s="5" t="inlineStr">
         <is>
           <t>316630004</t>
         </is>
       </c>
-      <c r="B330" s="2" t="inlineStr">
+      <c r="B330" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C330" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316630004</t>
-        </is>
-      </c>
-      <c r="D330" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316630004 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E330" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316630004. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F330" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G330" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H330" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I330" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C330" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316630004</t>
+        </is>
+      </c>
+      <c r="D330" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316630004 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E330" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316630004. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F330" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G330" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H330" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I330" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -14687,45 +14693,45 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="inlineStr">
+      <c r="A332" s="5" t="inlineStr">
         <is>
           <t>316442118</t>
         </is>
       </c>
-      <c r="B332" s="2" t="inlineStr">
+      <c r="B332" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C332" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316442118</t>
-        </is>
-      </c>
-      <c r="D332" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316442118 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E332" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316442118. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F332" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G332" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H332" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I332" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C332" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316442118</t>
+        </is>
+      </c>
+      <c r="D332" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316442118 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E332" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316442118. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F332" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G332" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H332" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I332" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -19546,88 +19552,88 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="2" t="inlineStr">
+      <c r="A445" s="5" t="inlineStr">
         <is>
           <t>316418501</t>
         </is>
       </c>
-      <c r="B445" s="2" t="inlineStr">
+      <c r="B445" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C445" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316418501</t>
-        </is>
-      </c>
-      <c r="D445" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316418501 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E445" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316418501. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F445" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G445" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H445" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I445" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C445" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316418501</t>
+        </is>
+      </c>
+      <c r="D445" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316418501 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E445" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316418501. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F445" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G445" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H445" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I445" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="2" t="inlineStr">
+      <c r="A446" s="5" t="inlineStr">
         <is>
           <t>316442118</t>
         </is>
       </c>
-      <c r="B446" s="2" t="inlineStr">
+      <c r="B446" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C446" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316442118</t>
-        </is>
-      </c>
-      <c r="D446" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316442118 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E446" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316442118. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F446" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G446" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H446" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I446" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C446" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316442118</t>
+        </is>
+      </c>
+      <c r="D446" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316442118 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E446" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316442118. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F446" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G446" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H446" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I446" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -19675,45 +19681,45 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="2" t="inlineStr">
+      <c r="A448" s="5" t="inlineStr">
         <is>
           <t>316456238</t>
         </is>
       </c>
-      <c r="B448" s="2" t="inlineStr">
+      <c r="B448" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C448" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316456238</t>
-        </is>
-      </c>
-      <c r="D448" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316456238 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E448" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316456238. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F448" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G448" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H448" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I448" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C448" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316456238</t>
+        </is>
+      </c>
+      <c r="D448" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316456238 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E448" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316456238. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F448" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G448" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H448" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I448" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -19761,303 +19767,303 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="2" t="inlineStr">
+      <c r="A450" s="5" t="inlineStr">
         <is>
           <t>316462890</t>
         </is>
       </c>
-      <c r="B450" s="2" t="inlineStr">
+      <c r="B450" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C450" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316462890</t>
-        </is>
-      </c>
-      <c r="D450" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316462890 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E450" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316462890. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F450" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G450" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H450" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I450" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C450" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316462890</t>
+        </is>
+      </c>
+      <c r="D450" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316462890 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E450" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316462890. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F450" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G450" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H450" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I450" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="2" t="inlineStr">
+      <c r="A451" s="5" t="inlineStr">
         <is>
           <t>316472803</t>
         </is>
       </c>
-      <c r="B451" s="2" t="inlineStr">
+      <c r="B451" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C451" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316472803</t>
-        </is>
-      </c>
-      <c r="D451" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316472803 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E451" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316472803. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F451" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G451" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H451" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I451" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C451" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316472803</t>
+        </is>
+      </c>
+      <c r="D451" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316472803 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E451" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316472803. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F451" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G451" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H451" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I451" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="2" t="inlineStr">
+      <c r="A452" s="5" t="inlineStr">
         <is>
           <t>316453036</t>
         </is>
       </c>
-      <c r="B452" s="2" t="inlineStr">
+      <c r="B452" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C452" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316453036</t>
-        </is>
-      </c>
-      <c r="D452" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316453036 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E452" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316453036. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F452" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G452" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H452" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I452" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C452" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316453036</t>
+        </is>
+      </c>
+      <c r="D452" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316453036 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E452" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316453036. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F452" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G452" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H452" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I452" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="2" t="inlineStr">
+      <c r="A453" s="5" t="inlineStr">
         <is>
           <t>316531983</t>
         </is>
       </c>
-      <c r="B453" s="2" t="inlineStr">
+      <c r="B453" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C453" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316531983</t>
-        </is>
-      </c>
-      <c r="D453" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316531983 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E453" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316531983. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F453" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G453" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H453" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I453" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C453" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316531983</t>
+        </is>
+      </c>
+      <c r="D453" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316531983 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E453" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316531983. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F453" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G453" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H453" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I453" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="2" t="inlineStr">
+      <c r="A454" s="5" t="inlineStr">
         <is>
           <t>316462865</t>
         </is>
       </c>
-      <c r="B454" s="2" t="inlineStr">
+      <c r="B454" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C454" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316462865</t>
-        </is>
-      </c>
-      <c r="D454" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316462865 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E454" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316462865. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F454" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G454" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H454" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I454" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C454" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316462865</t>
+        </is>
+      </c>
+      <c r="D454" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316462865 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E454" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316462865. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F454" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G454" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H454" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I454" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="2" t="inlineStr">
+      <c r="A455" s="5" t="inlineStr">
         <is>
           <t>316462878</t>
         </is>
       </c>
-      <c r="B455" s="2" t="inlineStr">
+      <c r="B455" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C455" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316462878</t>
-        </is>
-      </c>
-      <c r="D455" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316462878 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E455" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316462878. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F455" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G455" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H455" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I455" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C455" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316462878</t>
+        </is>
+      </c>
+      <c r="D455" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316462878 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E455" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316462878. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F455" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G455" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H455" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I455" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="2" t="inlineStr">
+      <c r="A456" s="5" t="inlineStr">
         <is>
           <t>316531960</t>
         </is>
       </c>
-      <c r="B456" s="2" t="inlineStr">
+      <c r="B456" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C456" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316531960</t>
-        </is>
-      </c>
-      <c r="D456" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316531960 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E456" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316531960. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F456" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G456" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H456" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I456" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C456" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316531960</t>
+        </is>
+      </c>
+      <c r="D456" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316531960 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E456" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316531960. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F456" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G456" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H456" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I456" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -20191,88 +20197,88 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="2" t="inlineStr">
+      <c r="A460" s="5" t="inlineStr">
         <is>
           <t>316650001</t>
         </is>
       </c>
-      <c r="B460" s="2" t="inlineStr">
+      <c r="B460" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C460" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316650001</t>
-        </is>
-      </c>
-      <c r="D460" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316650001 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E460" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316650001. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F460" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G460" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H460" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I460" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C460" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316650001</t>
+        </is>
+      </c>
+      <c r="D460" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316650001 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E460" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316650001. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F460" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G460" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H460" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I460" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="2" t="inlineStr">
+      <c r="A461" s="5" t="inlineStr">
         <is>
           <t>316630004</t>
         </is>
       </c>
-      <c r="B461" s="2" t="inlineStr">
+      <c r="B461" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C461" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316630004</t>
-        </is>
-      </c>
-      <c r="D461" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316630004 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E461" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316630004. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F461" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G461" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H461" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I461" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C461" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316630004</t>
+        </is>
+      </c>
+      <c r="D461" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316630004 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E461" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316630004. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F461" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G461" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H461" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I461" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -20320,45 +20326,45 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="2" t="inlineStr">
+      <c r="A463" s="5" t="inlineStr">
         <is>
           <t>316630001</t>
         </is>
       </c>
-      <c r="B463" s="2" t="inlineStr">
+      <c r="B463" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C463" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316630001</t>
-        </is>
-      </c>
-      <c r="D463" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316630001 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E463" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316630001. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F463" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G463" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H463" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I463" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C463" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316630001</t>
+        </is>
+      </c>
+      <c r="D463" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316630001 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E463" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316630001. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F463" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G463" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H463" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I463" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -20406,131 +20412,131 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="2" t="inlineStr">
+      <c r="A465" s="5" t="inlineStr">
         <is>
           <t>318022001</t>
         </is>
       </c>
-      <c r="B465" s="2" t="inlineStr">
+      <c r="B465" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C465" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 318022001</t>
-        </is>
-      </c>
-      <c r="D465" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 318022001 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E465" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 318022001. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F465" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G465" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H465" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I465" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C465" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 318022001</t>
+        </is>
+      </c>
+      <c r="D465" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 318022001 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E465" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 318022001. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F465" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G465" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H465" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I465" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="2" t="inlineStr">
+      <c r="A466" s="5" t="inlineStr">
         <is>
           <t>318258201</t>
         </is>
       </c>
-      <c r="B466" s="2" t="inlineStr">
+      <c r="B466" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C466" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 318258201</t>
-        </is>
-      </c>
-      <c r="D466" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 318258201 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E466" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 318258201. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F466" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G466" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H466" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I466" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C466" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 318258201</t>
+        </is>
+      </c>
+      <c r="D466" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 318258201 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E466" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 318258201. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F466" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G466" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H466" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I466" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="2" t="inlineStr">
+      <c r="A467" s="5" t="inlineStr">
         <is>
           <t>318261301</t>
         </is>
       </c>
-      <c r="B467" s="2" t="inlineStr">
+      <c r="B467" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C467" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 318261301</t>
-        </is>
-      </c>
-      <c r="D467" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 318261301 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E467" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 318261301. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F467" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G467" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H467" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I467" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C467" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 318261301</t>
+        </is>
+      </c>
+      <c r="D467" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 318261301 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E467" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 318261301. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F467" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G467" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H467" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I467" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -21438,45 +21444,45 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="2" t="inlineStr">
+      <c r="A489" s="5" t="inlineStr">
         <is>
           <t>316650003</t>
         </is>
       </c>
-      <c r="B489" s="2" t="inlineStr">
+      <c r="B489" s="5" t="inlineStr">
         <is>
           <t>Frigidaire</t>
         </is>
       </c>
-      <c r="C489" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316650003</t>
-        </is>
-      </c>
-      <c r="D489" s="2" t="inlineStr">
-        <is>
-          <t>Frigidaire Replacement Part - 316650003 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E489" s="2" t="inlineStr">
-        <is>
-          <t>Shop Frigidaire Replacement Part - 316650003. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F489" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G489" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="H489" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I489" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C489" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316650003</t>
+        </is>
+      </c>
+      <c r="D489" s="5" t="inlineStr">
+        <is>
+          <t>Frigidaire Range Part - 316650003 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E489" s="5" t="inlineStr">
+        <is>
+          <t>Shop Frigidaire Range Part - 316650003. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F489" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="G489" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H489" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I489" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
@@ -21739,45 +21745,45 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="2" t="inlineStr">
+      <c r="A496" s="5" t="inlineStr">
         <is>
           <t>MEB63654003</t>
         </is>
       </c>
-      <c r="B496" s="2" t="inlineStr">
+      <c r="B496" s="5" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="C496" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - MEB63654003</t>
-        </is>
-      </c>
-      <c r="D496" s="2" t="inlineStr">
-        <is>
-          <t>LG Replacement Part - MEB63654003 | OEM Part</t>
-        </is>
-      </c>
-      <c r="E496" s="2" t="inlineStr">
-        <is>
-          <t>Shop LG Replacement Part - MEB63654003. Replacement part - confirm fitment with your model number before ordering.</t>
-        </is>
-      </c>
-      <c r="F496" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G496" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="H496" s="2" t="inlineStr">
-        <is>
-          <t>Generic</t>
-        </is>
-      </c>
-      <c r="I496" s="2" t="inlineStr">
-        <is>
-          <t>Part type not identified - placeholder title; replace once description is known</t>
+      <c r="C496" s="5" t="inlineStr">
+        <is>
+          <t>LG Handle - MEB63654003</t>
+        </is>
+      </c>
+      <c r="D496" s="5" t="inlineStr">
+        <is>
+          <t>LG Handle - MEB63654003 | OEM Part</t>
+        </is>
+      </c>
+      <c r="E496" s="5" t="inlineStr">
+        <is>
+          <t>Shop LG Handle - MEB63654003. OEM replacement part. Confirm fitment with your model number before ordering.</t>
+        </is>
+      </c>
+      <c r="F496" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="G496" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="H496" s="5" t="inlineStr">
+        <is>
+          <t>Inferred</t>
+        </is>
+      </c>
+      <c r="I496" s="5" t="inlineStr">
+        <is>
+          <t>Part type INFERRED from part-number family (sibling numbers in the same series); exact part not confirmed - verify before publishing</t>
         </is>
       </c>
     </row>
